--- a/Supalai_Rama8_Price_Track.xlsx
+++ b/Supalai_Rama8_Price_Track.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Listings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Unit (~35sqm 1BR)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Listings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="My Unit (~35sqm 1BR)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Run Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$1</definedName>

--- a/Supalai_Rama8_Price_Track.xlsx
+++ b/Supalai_Rama8_Price_Track.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Run Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'My Unit (~35sqm 1BR)'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$1:$J$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,11 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -451,11 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -466,10 +467,10 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,8 +555,116 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>88983</v>
+      </c>
+      <c r="F2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>LivingInsider</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187152</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>s59.0_f14_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>89393</v>
+      </c>
+      <c r="F3" t="n">
+        <v>66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>LivingInsider</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187146</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>s66.0_f6_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -588,82 +697,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>First Seen</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Last Seen</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Listed (YYYY-MM)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Price (THB)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Price/sqm (THB)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Size (sqm)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Bedrooms</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Bathrooms</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Furnishing</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Listing Title</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Source(s)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>URL(s)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Unit Fingerprint</t>
         </is>
@@ -681,17 +790,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="n"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Run Date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Total Listings</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>My Unit Matches</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Overall Min Price</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Overall Max Price</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Overall Avg Price</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>My Unit Min Price</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>My Unit Avg Price</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>My Unit Max Price</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Sources Scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5575000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>LivingInsider</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Supalai_Rama8_Price_Track.xlsx
+++ b/Supalai_Rama8_Price_Track.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Run Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'My Unit (~35sqm 1BR)'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$1:$J$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -467,10 +467,10 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,30 +558,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5250000</v>
+        <v>1790000</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>88983</v>
+        <v>57741</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
-      </c>
-      <c r="G2" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -590,81 +587,594 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
+          <t>พัชรินทร์ พิศาลไพโรจน์</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>LivingInsider</t>
+          <t>DDproperty</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187152</t>
+          <t>https://www.ddproperty.com/en/agent/%E0%B8%9E%E0%B8%B1%E0%B8%8A%E0%B8%A3%E0%B8%B4%E0%B8%99%E0%B8%97%E0%B8%A3%E0%B9%8C-%E0%B8%9E%E0%B8%B4%E0%B8%A8%E0%B8%B2%E0%B8%A5%E0%B9%84%E0%B8%9E%E0%B9%82%E0%B8%A3%E0%B8%88%E0%B8%99%E0%B9%8C-12256</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>s59.0_f14_brNone_baNone</t>
+          <t>s31.0_fNone_brNone_baNone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>56756</v>
+      </c>
+      <c r="F3" t="n">
+        <v>37</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Ratchada-Huaykwang, Bangkok</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>s37.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2390000</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>53111</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Ratchada-Huaykwang, Bangkok</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>s45.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/pattamanan-pongnoparat-17602753 | https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>s35.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>70833</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Pichamon Boonchit</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/pichamon-boonchit-14459021 | https://www.ddproperty.com/en/agent/sanick-sawaisanyakorn-14447205 | https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>s36.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>73404</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>s47.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>80434</v>
+      </c>
+      <c r="F8" t="n">
+        <v>46</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/jesadakorn-cohn-14458669 | https://www.ddproperty.com/en/agent/bussara-sri-at-14447364</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>s46.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Ratchada-Huaykwang, Bangkok</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>s60.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3990000</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Bencharong (Yok) Treerat-a-na-wat</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/bencharong-yok)-treerat-a-na-wat-14293651 | https://www.ddproperty.com/en/agent/homemark-2309099</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>s57.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>86486</v>
+      </c>
+      <c r="F11" t="n">
+        <v>74</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>s74.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D12" s="2" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>88983</v>
+      </c>
+      <c r="F12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>LivingInsider</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187152</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>s59.0_f14_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>5900000</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>89393</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F13" t="n">
         <v>66</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G13" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>LivingInsider</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187146</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>s66.0_f6_brNone_baNone</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P3"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -790,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -860,32 +1370,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>1790000</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3272000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>5250000</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>5900000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>5575000</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>LivingInsider</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Supalai_Rama8_Price_Track.xlsx
+++ b/Supalai_Rama8_Price_Track.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Run Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Listings'!$A$1:$P$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'My Unit (~35sqm 1BR)'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run Summary'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -762,12 +762,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2550000</v>
+        <v>2600000</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>70833</v>
+        <v>68421</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Pichamon Boonchit</t>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.ddproperty.com/en/agent/pichamon-boonchit-14459021 | https://www.ddproperty.com/en/agent/sanick-sawaisanyakorn-14447205 | https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+          <t>https://www.ddproperty.com/en/agent/homemark-2309099</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>s36.0_fNone_brNone_baNone</t>
+          <t>s38.0_fNone_brNone_baNone</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -864,12 +864,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3700000</v>
+        <v>3820000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80434</v>
+        <v>83043</v>
       </c>
       <c r="F8" t="n">
         <v>46</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6400000</v>
+        <v>4000000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>86486</v>
+        <v>64516</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Supalai City Resort Rama 8, Bangkok</t>
+          <t>Sirirut Havee Akehurst</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1056,42 +1056,39 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+          <t>https://www.ddproperty.com/en/agent/sirirut-havee-akehurst-17834001</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>s74.0_fNone_brNone_baNone</t>
+          <t>s62.0_fNone_brNone_baNone</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5250000</v>
+        <v>6400000</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>88983</v>
+        <v>86486</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
-      </c>
-      <c r="G12" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1100,81 +1097,237 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>LivingInsider</t>
+          <t>DDproperty</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187152</t>
+          <t>https://www.ddproperty.com/en/agent/connex-property-13504900</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>s59.0_f14_brNone_baNone</t>
+          <t>s74.0_fNone_brNone_baNone</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>70833</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Pichamon Boonchit</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/pichamon-boonchit-14459021 | https://www.ddproperty.com/en/agent/sanick-sawaisanyakorn-14447205 | https://www.ddproperty.com/en/agent/connex-property-13504900</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>s36.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>80434</v>
+      </c>
+      <c r="F14" t="n">
+        <v>46</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Supalai City Resort Rama 8, Bangkok</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://www.ddproperty.com/en/agent/jesadakorn-cohn-14458669 | https://www.ddproperty.com/en/agent/bussara-sri-at-14447364</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>s46.0_fNone_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>88983</v>
+      </c>
+      <c r="F15" t="n">
+        <v>59</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>LivingInsider</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187152</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>s59.0_f14_brNone_baNone</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>5900000</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>89393</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F16" t="n">
         <v>66</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G16" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>🔥 ขายด่วน!! คอนโด Supalai Veranda Ramkhamhaeng</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>LivingInsider</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>https://www.livinginsider.com/detail/condo-for-sale-condo-supalai-veranda-ramkhamheang-2bedroom-2187146</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>s66.0_f6_brNone_baNone</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:P16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1300,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1370,11 +1523,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1386,7 +1539,7 @@
         <v>6400000</v>
       </c>
       <c r="F2" t="n">
-        <v>3272000</v>
+        <v>3353636</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1397,7 +1550,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1407,22 +1560,49 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3125000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DDproperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>5250000</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>5900000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>5575000</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>LivingInsider</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>